--- a/Excel/LookupFunctions8001.xlsx
+++ b/Excel/LookupFunctions8001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\ANP-D8001\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D85180F-903D-4055-9A71-F4DB09F27A6A}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA802F0-ECC4-4BFF-AD2D-A95BF670EE1A}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8140" xr2:uid="{50D84799-CBF3-484B-A582-8F0336BCC462}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8140" activeTab="1" xr2:uid="{50D84799-CBF3-484B-A582-8F0336BCC462}"/>
   </bookViews>
   <sheets>
     <sheet name="RawData" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="193">
   <si>
     <t>Student Code</t>
   </si>
@@ -599,6 +599,12 @@
   </si>
   <si>
     <t>keerthinandinipepakayala@gmail.com</t>
+  </si>
+  <si>
+    <t>Vlookup Limitations</t>
+  </si>
+  <si>
+    <t>1. if we have more number of columns figuring out the column number would be tough</t>
   </si>
 </sst>
 </file>
@@ -674,12 +680,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12958,44 +12976,71 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D3F3E36-1C13-48FD-BE7F-B8C4F48669BB}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.90625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="7.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" t="str">
+      <c r="F1" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="B2" s="7" t="str">
         <f>VLOOKUP(A2,RawData!$A$2:$I$46,2,FALSE)</f>
-        <v>Manda srujana</v>
+        <v>Badikela Sai Ruchith</v>
+      </c>
+      <c r="C2" s="5">
+        <f>VLOOKUP(A2,RawData!$A$2:$I$46,3,FALSE)</f>
+        <v>37338</v>
+      </c>
+      <c r="D2" s="7" t="str">
+        <f>VLOOKUP($A$2,RawData!$A$2:$I$46,4,FALSE)</f>
+        <v>male</v>
+      </c>
+      <c r="E2" s="7" t="str">
+        <f>VLOOKUP($A$2,RawData!$A$2:$I$46,5,FALSE)</f>
+        <v>venkatesh</v>
+      </c>
+      <c r="F2" s="7">
+        <f>VLOOKUP($A$2,RawData!$A$2:$I$46,9,FALSE)</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B6" s="7" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B7" s="8" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/LookupFunctions8001.xlsx
+++ b/Excel/LookupFunctions8001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\ANP-D8001\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D62A36-8127-45A3-A1EC-45B6568829C5}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E26D0A-6747-414A-A230-1185EB485100}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8140" firstSheet="1" activeTab="6" xr2:uid="{50D84799-CBF3-484B-A582-8F0336BCC462}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="208">
   <si>
     <t>Student Code</t>
   </si>
@@ -688,6 +688,9 @@
   </si>
   <si>
     <t>the above formulas will work but not dynamic</t>
+  </si>
+  <si>
+    <t>AFID</t>
   </si>
 </sst>
 </file>
@@ -16363,21 +16366,22 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBC5F9A9-2B69-4072-860C-B9124F9D8BDC}">
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -16391,22 +16395,25 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -16420,22 +16427,25 @@
         <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="1">
+      <c r="H2" s="1">
         <v>35000</v>
       </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
         <v>5</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2" s="1">
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -16449,22 +16459,25 @@
         <v>16</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="1">
+      <c r="H3" s="1">
         <v>12000</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
         <v>5</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
@@ -16478,22 +16491,25 @@
         <v>11</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1">
         <v>15000</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <v>4</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4" s="1">
         <v>2024</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>23</v>
       </c>
@@ -16507,22 +16523,25 @@
         <v>16</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>15000</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>8</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>27</v>
       </c>
@@ -16536,22 +16555,25 @@
         <v>16</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>20000</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>4</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
@@ -16565,22 +16587,25 @@
         <v>16</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>24949</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>4</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>35</v>
       </c>
@@ -16594,22 +16619,25 @@
         <v>16</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>15000</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>8</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>39</v>
       </c>
@@ -16623,22 +16651,25 @@
         <v>11</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>15000</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <v>7</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>43</v>
       </c>
@@ -16652,22 +16683,25 @@
         <v>16</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <v>29980</v>
       </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
         <v>4</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>47</v>
       </c>
@@ -16681,22 +16715,25 @@
         <v>16</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <v>10000</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <v>1</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>51</v>
       </c>
@@ -16710,22 +16747,25 @@
         <v>16</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G12" s="1">
+      <c r="H12" s="1">
         <v>15000</v>
       </c>
-      <c r="H12" s="1">
+      <c r="I12" s="1">
         <v>4</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>55</v>
       </c>
@@ -16739,22 +16779,25 @@
         <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G13" s="1">
+      <c r="H13" s="1">
         <v>35000</v>
       </c>
-      <c r="H13" s="1">
+      <c r="I13" s="1">
         <v>4</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>59</v>
       </c>
@@ -16768,22 +16811,25 @@
         <v>16</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G14" s="1">
+      <c r="H14" s="1">
         <v>15000</v>
       </c>
-      <c r="H14" s="1">
+      <c r="I14" s="1">
         <v>4</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>63</v>
       </c>
@@ -16797,22 +16843,25 @@
         <v>16</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G15" s="1">
+      <c r="H15" s="1">
         <v>15000</v>
       </c>
-      <c r="H15" s="1">
+      <c r="I15" s="1">
         <v>4</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>67</v>
       </c>
@@ -16826,22 +16875,25 @@
         <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="G16" s="1">
+      <c r="H16" s="1">
         <v>30000</v>
       </c>
-      <c r="H16" s="1">
+      <c r="I16" s="1">
         <v>4</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>71</v>
       </c>
@@ -16855,22 +16907,25 @@
         <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="G17" s="1">
+      <c r="H17" s="1">
         <v>30000</v>
       </c>
-      <c r="H17" s="1">
+      <c r="I17" s="1">
         <v>4</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J17" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>75</v>
       </c>
@@ -16884,22 +16939,25 @@
         <v>16</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="G18" s="1">
+      <c r="H18" s="1">
         <v>20000</v>
       </c>
-      <c r="H18" s="1">
+      <c r="I18" s="1">
         <v>5</v>
       </c>
-      <c r="I18" s="1">
+      <c r="J18" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>79</v>
       </c>
@@ -16913,22 +16971,25 @@
         <v>16</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="G19" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G19" s="1">
+      <c r="H19" s="1">
         <v>30000</v>
       </c>
-      <c r="H19" s="1">
+      <c r="I19" s="1">
         <v>5</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>83</v>
       </c>
@@ -16942,22 +17003,25 @@
         <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="G20" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G20" s="1">
+      <c r="H20" s="1">
         <v>15000</v>
       </c>
-      <c r="H20" s="1">
+      <c r="I20" s="1">
         <v>4</v>
       </c>
-      <c r="I20" s="1">
+      <c r="J20" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>87</v>
       </c>
@@ -16971,22 +17035,25 @@
         <v>16</v>
       </c>
       <c r="E21" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="G21" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G21" s="1">
+      <c r="H21" s="1">
         <v>20000</v>
       </c>
-      <c r="H21" s="1">
+      <c r="I21" s="1">
         <v>3</v>
       </c>
-      <c r="I21" s="1">
+      <c r="J21" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
         <v>91</v>
       </c>
@@ -17000,22 +17067,25 @@
         <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="G22" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G22" s="1">
+      <c r="H22" s="1">
         <v>19976</v>
       </c>
-      <c r="H22" s="1">
+      <c r="I22" s="1">
         <v>5</v>
       </c>
-      <c r="I22" s="1">
+      <c r="J22" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
         <v>95</v>
       </c>
@@ -17029,22 +17099,25 @@
         <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="G23" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G23" s="1">
+      <c r="H23" s="1">
         <v>27991</v>
       </c>
-      <c r="H23" s="1">
+      <c r="I23" s="1">
         <v>4</v>
       </c>
-      <c r="I23" s="1">
+      <c r="J23" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
         <v>99</v>
       </c>
@@ -17058,22 +17131,25 @@
         <v>16</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="G24" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="G24" s="1">
+      <c r="H24" s="1">
         <v>40000</v>
       </c>
-      <c r="H24" s="1">
+      <c r="I24" s="1">
         <v>5</v>
       </c>
-      <c r="I24" s="1">
+      <c r="J24" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
         <v>103</v>
       </c>
@@ -17087,22 +17163,25 @@
         <v>16</v>
       </c>
       <c r="E25" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="G25" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="G25" s="1">
+      <c r="H25" s="1">
         <v>10000</v>
       </c>
-      <c r="H25" s="1">
+      <c r="I25" s="1">
         <v>5</v>
       </c>
-      <c r="I25" s="1">
+      <c r="J25" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
         <v>107</v>
       </c>
@@ -17116,22 +17195,25 @@
         <v>16</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="G26" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="G26" s="1">
+      <c r="H26" s="1">
         <v>15000</v>
       </c>
-      <c r="H26" s="1">
+      <c r="I26" s="1">
         <v>5</v>
       </c>
-      <c r="I26" s="1">
+      <c r="J26" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
         <v>111</v>
       </c>
@@ -17145,22 +17227,25 @@
         <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="G27" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G27" s="1">
+      <c r="H27" s="1">
         <v>15000</v>
       </c>
-      <c r="H27" s="1">
+      <c r="I27" s="1">
         <v>7</v>
       </c>
-      <c r="I27" s="1">
+      <c r="J27" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
         <v>115</v>
       </c>
@@ -17174,22 +17259,25 @@
         <v>16</v>
       </c>
       <c r="E28" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="G28" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G28" s="1">
+      <c r="H28" s="1">
         <v>10000</v>
       </c>
-      <c r="H28" s="1">
+      <c r="I28" s="1">
         <v>4</v>
       </c>
-      <c r="I28" s="1">
+      <c r="J28" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
         <v>119</v>
       </c>
@@ -17203,22 +17291,25 @@
         <v>11</v>
       </c>
       <c r="E29" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="G29" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="G29" s="1">
+      <c r="H29" s="1">
         <v>40000</v>
       </c>
-      <c r="H29" s="1">
+      <c r="I29" s="1">
         <v>3</v>
       </c>
-      <c r="I29" s="1">
+      <c r="J29" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
         <v>123</v>
       </c>
@@ -17232,22 +17323,25 @@
         <v>16</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="G30" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G30" s="1">
+      <c r="H30" s="1">
         <v>25000</v>
       </c>
-      <c r="H30" s="1">
+      <c r="I30" s="1">
         <v>4</v>
       </c>
-      <c r="I30" s="1">
+      <c r="J30" s="1">
         <v>2020</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
         <v>127</v>
       </c>
@@ -17261,22 +17355,25 @@
         <v>16</v>
       </c>
       <c r="E31" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="G31" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="G31" s="1">
+      <c r="H31" s="1">
         <v>45000</v>
       </c>
-      <c r="H31" s="1">
+      <c r="I31" s="1">
         <v>4</v>
       </c>
-      <c r="I31" s="1">
+      <c r="J31" s="1">
         <v>2024</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
         <v>131</v>
       </c>
@@ -17290,22 +17387,25 @@
         <v>16</v>
       </c>
       <c r="E32" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="G32" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="G32" s="1">
+      <c r="H32" s="1">
         <v>24000</v>
       </c>
-      <c r="H32" s="1">
+      <c r="I32" s="1">
         <v>4</v>
       </c>
-      <c r="I32" s="1">
+      <c r="J32" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
         <v>135</v>
       </c>
@@ -17319,22 +17419,25 @@
         <v>16</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="G33" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="G33" s="1">
+      <c r="H33" s="1">
         <v>10000</v>
       </c>
-      <c r="H33" s="1">
+      <c r="I33" s="1">
         <v>4</v>
       </c>
-      <c r="I33" s="1">
+      <c r="J33" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
         <v>139</v>
       </c>
@@ -17348,22 +17451,25 @@
         <v>11</v>
       </c>
       <c r="E34" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="G34" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="G34" s="1">
+      <c r="H34" s="1">
         <v>10000</v>
       </c>
-      <c r="H34" s="1">
+      <c r="I34" s="1">
         <v>2</v>
       </c>
-      <c r="I34" s="1">
+      <c r="J34" s="1">
         <v>2023</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
         <v>143</v>
       </c>
@@ -17377,22 +17483,25 @@
         <v>16</v>
       </c>
       <c r="E35" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="G35" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="G35" s="1">
+      <c r="H35" s="1">
         <v>15000</v>
       </c>
-      <c r="H35" s="1">
+      <c r="I35" s="1">
         <v>4</v>
       </c>
-      <c r="I35" s="1">
+      <c r="J35" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
         <v>147</v>
       </c>
@@ -17406,22 +17515,25 @@
         <v>11</v>
       </c>
       <c r="E36" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="G36" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="G36" s="1">
+      <c r="H36" s="1">
         <v>20000</v>
       </c>
-      <c r="H36" s="1">
+      <c r="I36" s="1">
         <v>4</v>
       </c>
-      <c r="I36" s="1">
+      <c r="J36" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
         <v>151</v>
       </c>
@@ -17435,22 +17547,25 @@
         <v>11</v>
       </c>
       <c r="E37" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="G37" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="G37" s="1">
+      <c r="H37" s="1">
         <v>15000</v>
       </c>
-      <c r="H37" s="1">
+      <c r="I37" s="1">
         <v>5</v>
       </c>
-      <c r="I37" s="1">
+      <c r="J37" s="1">
         <v>2024</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
         <v>155</v>
       </c>
@@ -17464,22 +17579,25 @@
         <v>11</v>
       </c>
       <c r="E38" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="G38" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="G38" s="1">
+      <c r="H38" s="1">
         <v>16000</v>
       </c>
-      <c r="H38" s="1">
+      <c r="I38" s="1">
         <v>6</v>
       </c>
-      <c r="I38" s="1">
+      <c r="J38" s="1">
         <v>2024</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
         <v>159</v>
       </c>
@@ -17493,22 +17611,25 @@
         <v>11</v>
       </c>
       <c r="E39" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="G39" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="G39" s="1">
+      <c r="H39" s="1">
         <v>9000</v>
       </c>
-      <c r="H39" s="1">
+      <c r="I39" s="1">
         <v>4</v>
       </c>
-      <c r="I39" s="1">
+      <c r="J39" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
         <v>163</v>
       </c>
@@ -17522,22 +17643,25 @@
         <v>16</v>
       </c>
       <c r="E40" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="G40" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="G40" s="1">
+      <c r="H40" s="1">
         <v>16000</v>
       </c>
-      <c r="H40" s="1">
+      <c r="I40" s="1">
         <v>4</v>
       </c>
-      <c r="I40" s="1">
+      <c r="J40" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
         <v>167</v>
       </c>
@@ -17551,22 +17675,25 @@
         <v>11</v>
       </c>
       <c r="E41" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="G41" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="G41" s="1">
+      <c r="H41" s="1">
         <v>17000</v>
       </c>
-      <c r="H41" s="1">
+      <c r="I41" s="1">
         <v>4</v>
       </c>
-      <c r="I41" s="1">
+      <c r="J41" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
         <v>171</v>
       </c>
@@ -17580,22 +17707,25 @@
         <v>11</v>
       </c>
       <c r="E42" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="G42" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="G42" s="1">
+      <c r="H42" s="1">
         <v>60000</v>
       </c>
-      <c r="H42" s="1">
+      <c r="I42" s="1">
         <v>3</v>
       </c>
-      <c r="I42" s="1">
+      <c r="J42" s="1">
         <v>2024</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="1" t="s">
         <v>175</v>
       </c>
@@ -17609,22 +17739,25 @@
         <v>16</v>
       </c>
       <c r="E43" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="G43" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="G43" s="1">
+      <c r="H43" s="1">
         <v>25000</v>
       </c>
-      <c r="H43" s="1">
+      <c r="I43" s="1">
         <v>4</v>
       </c>
-      <c r="I43" s="1">
+      <c r="J43" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="1" t="s">
         <v>179</v>
       </c>
@@ -17638,22 +17771,25 @@
         <v>16</v>
       </c>
       <c r="E44" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="G44" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="G44" s="1">
+      <c r="H44" s="1">
         <v>15000</v>
       </c>
-      <c r="H44" s="1">
+      <c r="I44" s="1">
         <v>4</v>
       </c>
-      <c r="I44" s="1">
+      <c r="J44" s="1">
         <v>2024</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="1" t="s">
         <v>183</v>
       </c>
@@ -17667,22 +17803,25 @@
         <v>16</v>
       </c>
       <c r="E45" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="G45" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="G45" s="1">
+      <c r="H45" s="1">
         <v>15000</v>
       </c>
-      <c r="H45" s="1">
+      <c r="I45" s="1">
         <v>4</v>
       </c>
-      <c r="I45" s="1">
+      <c r="J45" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="1" t="s">
         <v>187</v>
       </c>
@@ -17696,18 +17835,21 @@
         <v>16</v>
       </c>
       <c r="E46" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="G46" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="G46" s="1">
+      <c r="H46" s="1">
         <v>25000</v>
       </c>
-      <c r="H46" s="1">
+      <c r="I46" s="1">
         <v>4</v>
       </c>
-      <c r="I46" s="1">
+      <c r="J46" s="1">
         <v>2025</v>
       </c>
     </row>
@@ -17719,12 +17861,12 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9782EBA-4EBE-486A-AC9C-72CC4C025E26}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.6328125" customWidth="1"/>
-    <col min="2" max="2" width="19.54296875" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.4">
@@ -17743,11 +17885,11 @@
         <v>35</v>
       </c>
       <c r="B2" s="14" t="str">
-        <f>INDEX(IandMData!$A$2:$I$46,5,2)</f>
+        <f>INDEX(IandMData!$A$2:$J$46,5,2)</f>
         <v>Nagapuri sai sree</v>
       </c>
       <c r="C2" s="2">
-        <f>INDEX(IandMData!$A$2:$I$46,5,3)</f>
+        <f>INDEX(IandMData!$A$2:$J$46,5,3)</f>
         <v>37714</v>
       </c>
     </row>
@@ -17793,12 +17935,71 @@
         <v>9</v>
       </c>
       <c r="B12" s="14" t="str">
-        <f>INDEX(IandMData!$A$2:$I$46,MATCH(A12,IandMData!$A2:$A1000,0),2)</f>
+        <f>INDEX(IandMData!$A$2:$J$46,MATCH(A12,IandMData!$A2:$A1000,0),2)</f>
         <v>Vutukuru Sri Naga Sai Koundinya</v>
       </c>
       <c r="C12" s="2">
-        <f>INDEX(IandMData!$A$2:$I$46,MATCH(A12,IandMData!$A2:$A1000,0),3)</f>
+        <f>INDEX(IandMData!$A$2:$J$46,MATCH(A12,IandMData!$A2:$A1000,0),3)</f>
         <v>37832</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="7">
+        <f>MATCH(A16,IandMData!$1:$1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="B17" s="7">
+        <f>MATCH(B16,IandMData!$1:$1,0)</f>
+        <v>2</v>
+      </c>
+      <c r="C17" s="7">
+        <f>MATCH(C16,IandMData!$1:$1,0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="str">
+        <f>INDEX(IandMData!$A$1:$J$46,MATCH(IndexAndMatch!$A$18,IandMData!$A$2:$A$46,0),MATCH($B$16,IandMData!$1:$1,0))</f>
+        <v>Vutukuru Sri Naga Sai Koundinya</v>
+      </c>
+      <c r="C18" s="2">
+        <f>INDEX(IandMData!$A$1:$J$46,MATCH(IndexAndMatch!$A$18,IandMData!$A$2:$A$46,0),MATCH($C$16,IandMData!$1:$1,0))</f>
+        <v>37832</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="20" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="str">
+        <f>INDEX(IandMData!$A$2:$J$46,MATCH(IndexAndMatch!$A$21,IandMData!$E$2:$E$46,0),MATCH(IndexAndMatch!B$20,IandMData!$1:$1,0))</f>
+        <v>Akshitha Namthebad</v>
       </c>
     </row>
   </sheetData>
@@ -17806,12 +18007,12 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9D16D99B-C5D6-488A-A899-574E89B6F332}">
           <x14:formula1>
             <xm:f>IandMData!$A$2:$A$46</xm:f>
           </x14:formula1>
-          <xm:sqref>A8 A12</xm:sqref>
+          <xm:sqref>A8 A12 A18 A21</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
